--- a/grupos/4AEV - Estadisticos 20232.xlsx
+++ b/grupos/4AEV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="88">
   <si>
     <t>Materia</t>
   </si>
@@ -164,21 +164,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Sanchez Hernández Raymundo</t>
+  </si>
+  <si>
+    <t>Urias Morales Alejandra</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Urias Morales Alejandra</t>
-  </si>
-  <si>
-    <t>Sanchez Hernández Raymundo</t>
-  </si>
-  <si>
     <t>Flores Paz Victor</t>
   </si>
   <si>
@@ -194,70 +194,94 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>CAMPOS</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>LOBATO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
     <t>PLIEGO</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>GERSON</t>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>MARCO</t>
   </si>
   <si>
     <t>DAVID</t>
   </si>
   <si>
+    <t>CRISTIAN OSMAR</t>
+  </si>
+  <si>
+    <t>ERIK OMAR</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
     <t>FABIAN ALEJANDRO</t>
   </si>
   <si>
-    <t>LEONEL FELIPE</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
     <t>JAIRO YAIR</t>
   </si>
   <si>
-    <t>ABDIEL NOE</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>ERIK</t>
   </si>
 </sst>
 </file>
@@ -784,25 +808,25 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -826,22 +850,22 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA4">
         <v>8</v>
       </c>
       <c r="AB4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC4">
         <v>5</v>
@@ -873,25 +897,25 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -915,22 +939,22 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -962,25 +986,25 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1004,13 +1028,13 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z6">
         <v>9</v>
@@ -1022,7 +1046,7 @@
         <v>10</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1051,25 +1075,25 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1102,13 +1126,13 @@
         <v>5</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC7">
         <v>5</v>
@@ -1140,25 +1164,25 @@
         <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1185,19 +1209,19 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA8">
         <v>8</v>
       </c>
       <c r="AB8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC8">
         <v>7</v>
@@ -1229,25 +1253,25 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1277,16 +1301,16 @@
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC9">
         <v>7</v>
@@ -1318,25 +1342,25 @@
         <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1360,22 +1384,22 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC10">
         <v>7</v>
@@ -1407,25 +1431,25 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1455,7 +1479,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z11">
         <v>9</v>
@@ -1496,25 +1520,25 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1538,25 +1562,25 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA12">
         <v>7</v>
       </c>
       <c r="AB12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1585,25 +1609,25 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1627,13 +1651,13 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>5</v>
@@ -1645,7 +1669,7 @@
         <v>7</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1674,25 +1698,25 @@
         <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1719,10 +1743,10 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z14">
         <v>5</v>
@@ -1731,10 +1755,10 @@
         <v>8</v>
       </c>
       <c r="AB14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1763,25 +1787,25 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1805,13 +1829,13 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z15">
         <v>5</v>
@@ -1820,7 +1844,7 @@
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC15">
         <v>5</v>
@@ -1852,25 +1876,25 @@
         <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1894,19 +1918,19 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z16">
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB16">
         <v>8</v>
@@ -1941,25 +1965,25 @@
         <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1986,10 +2010,10 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z17">
         <v>6</v>
@@ -2030,25 +2054,25 @@
         <v>5</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2072,22 +2096,22 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z18">
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC18">
         <v>5</v>
@@ -2119,25 +2143,25 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2161,16 +2185,16 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>10</v>
@@ -2208,25 +2232,25 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2250,22 +2274,22 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC20">
         <v>6</v>
@@ -2297,25 +2321,25 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2339,25 +2363,25 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z21">
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2386,25 +2410,25 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2431,19 +2455,19 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>6</v>
@@ -2475,25 +2499,25 @@
         <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2517,22 +2541,22 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC23">
         <v>6</v>
@@ -2564,25 +2588,25 @@
         <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2606,22 +2630,22 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z24">
         <v>5</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>5</v>
@@ -2653,25 +2677,25 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2695,22 +2719,22 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC25">
         <v>5</v>
@@ -2742,25 +2766,25 @@
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2784,22 +2808,22 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC26">
         <v>5</v>
@@ -2953,46 +2977,46 @@
         <v>76</v>
       </c>
       <c r="I4">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J4">
-        <v>85</v>
+        <v>83.8</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="P4">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="Q4">
-        <v>85</v>
+        <v>83.8</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="S4">
         <v>100</v>
       </c>
       <c r="T4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U4">
         <v>100</v>
       </c>
       <c r="V4">
-        <v>76</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3021,46 +3045,46 @@
         <v>80</v>
       </c>
       <c r="I5">
-        <v>85</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="J5">
-        <v>85</v>
+        <v>83.8</v>
       </c>
       <c r="K5">
-        <v>85</v>
+        <v>87.8</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N5">
         <v>100</v>
       </c>
       <c r="O5">
-        <v>80</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="P5">
-        <v>85</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="Q5">
-        <v>85</v>
+        <v>83.8</v>
       </c>
       <c r="R5">
-        <v>85</v>
+        <v>87.8</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="T5">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U5">
         <v>100</v>
       </c>
       <c r="V5">
-        <v>80</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3107,7 +3131,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3128,7 +3152,7 @@
         <v>100</v>
       </c>
       <c r="V6">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3157,46 +3181,46 @@
         <v>72</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="J7">
-        <v>85</v>
+        <v>83.8</v>
       </c>
       <c r="K7">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="N7">
         <v>100</v>
       </c>
       <c r="O7">
-        <v>72</v>
+        <v>56.3</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="Q7">
-        <v>85</v>
+        <v>83.8</v>
       </c>
       <c r="R7">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="S7">
         <v>100</v>
       </c>
       <c r="T7">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="U7">
         <v>100</v>
       </c>
       <c r="V7">
-        <v>72</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3225,46 +3249,46 @@
         <v>88</v>
       </c>
       <c r="I8">
-        <v>85</v>
+        <v>90.2</v>
       </c>
       <c r="J8">
-        <v>95</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N8">
         <v>100</v>
       </c>
       <c r="O8">
-        <v>88</v>
+        <v>87.5</v>
       </c>
       <c r="P8">
-        <v>85</v>
+        <v>90.2</v>
       </c>
       <c r="Q8">
-        <v>95</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S8">
         <v>100</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="U8">
         <v>100</v>
       </c>
       <c r="V8">
-        <v>88</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3293,10 +3317,10 @@
         <v>88</v>
       </c>
       <c r="I9">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="J9">
-        <v>90</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -3305,19 +3329,19 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N9">
         <v>100</v>
       </c>
       <c r="O9">
-        <v>88</v>
+        <v>93.8</v>
       </c>
       <c r="P9">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q9">
-        <v>90</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -3326,13 +3350,13 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U9">
         <v>100</v>
       </c>
       <c r="V9">
-        <v>88</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3361,13 +3385,13 @@
         <v>88</v>
       </c>
       <c r="I10">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="J10">
-        <v>90</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -3379,16 +3403,16 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="P10">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q10">
-        <v>90</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="R10">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3400,7 +3424,7 @@
         <v>100</v>
       </c>
       <c r="V10">
-        <v>88</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3429,10 +3453,10 @@
         <v>96</v>
       </c>
       <c r="I11">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="J11">
-        <v>90</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -3441,34 +3465,34 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N11">
         <v>100</v>
       </c>
       <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="Q11">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
         <v>96</v>
       </c>
-      <c r="P11">
-        <v>95</v>
-      </c>
-      <c r="Q11">
-        <v>90</v>
-      </c>
-      <c r="R11">
-        <v>100</v>
-      </c>
-      <c r="S11">
-        <v>100</v>
-      </c>
-      <c r="T11">
-        <v>100</v>
-      </c>
       <c r="U11">
         <v>100</v>
       </c>
       <c r="V11">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3497,46 +3521,46 @@
         <v>88</v>
       </c>
       <c r="I12">
-        <v>95</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="J12">
-        <v>100</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>90.2</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="N12">
         <v>100</v>
       </c>
       <c r="O12">
-        <v>88</v>
+        <v>79.2</v>
       </c>
       <c r="P12">
-        <v>95</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>90.2</v>
       </c>
       <c r="S12">
         <v>100</v>
       </c>
       <c r="T12">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="U12">
         <v>100</v>
       </c>
       <c r="V12">
-        <v>88</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3565,46 +3589,46 @@
         <v>84</v>
       </c>
       <c r="I13">
-        <v>90</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="J13">
-        <v>90</v>
+        <v>86.5</v>
       </c>
       <c r="K13">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13">
-        <v>84</v>
+        <v>70.8</v>
       </c>
       <c r="P13">
-        <v>90</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Q13">
-        <v>90</v>
+        <v>86.5</v>
       </c>
       <c r="R13">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T13">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="U13">
         <v>100</v>
       </c>
       <c r="V13">
-        <v>84</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -3633,46 +3657,46 @@
         <v>68</v>
       </c>
       <c r="I14">
-        <v>90</v>
+        <v>80.5</v>
       </c>
       <c r="J14">
-        <v>95</v>
+        <v>89.2</v>
       </c>
       <c r="K14">
-        <v>90</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="N14">
         <v>100</v>
       </c>
       <c r="O14">
-        <v>68</v>
+        <v>66.7</v>
       </c>
       <c r="P14">
-        <v>90</v>
+        <v>80.5</v>
       </c>
       <c r="Q14">
-        <v>95</v>
+        <v>89.2</v>
       </c>
       <c r="R14">
-        <v>90</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T14">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="U14">
         <v>100</v>
       </c>
       <c r="V14">
-        <v>68</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3701,10 +3725,10 @@
         <v>84</v>
       </c>
       <c r="I15">
-        <v>90</v>
+        <v>87.8</v>
       </c>
       <c r="J15">
-        <v>90</v>
+        <v>86.5</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -3713,19 +3737,19 @@
         <v>100</v>
       </c>
       <c r="M15">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="N15">
         <v>100</v>
       </c>
       <c r="O15">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="P15">
-        <v>90</v>
+        <v>87.8</v>
       </c>
       <c r="Q15">
-        <v>90</v>
+        <v>86.5</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -3734,13 +3758,13 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="U15">
         <v>100</v>
       </c>
       <c r="V15">
-        <v>84</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -3769,46 +3793,46 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="J16">
-        <v>100</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="N16">
         <v>100</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="U16">
         <v>100</v>
       </c>
       <c r="V16">
-        <v>100</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3837,46 +3861,46 @@
         <v>84</v>
       </c>
       <c r="I17">
-        <v>90</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="J17">
-        <v>85</v>
+        <v>89.2</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>92.7</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N17">
         <v>100</v>
       </c>
       <c r="O17">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="P17">
-        <v>90</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="Q17">
-        <v>85</v>
+        <v>89.2</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>92.7</v>
       </c>
       <c r="S17">
         <v>100</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U17">
         <v>100</v>
       </c>
       <c r="V17">
-        <v>84</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -3905,46 +3929,46 @@
         <v>76</v>
       </c>
       <c r="I18">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="J18">
+        <v>97.3</v>
+      </c>
+      <c r="K18">
+        <v>87.8</v>
+      </c>
+      <c r="L18">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="M18">
         <v>90</v>
       </c>
-      <c r="J18">
-        <v>95</v>
-      </c>
-      <c r="K18">
+      <c r="N18">
+        <v>100</v>
+      </c>
+      <c r="O18">
+        <v>66.7</v>
+      </c>
+      <c r="P18">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="Q18">
+        <v>97.3</v>
+      </c>
+      <c r="R18">
+        <v>87.8</v>
+      </c>
+      <c r="S18">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="T18">
         <v>90</v>
       </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
-      <c r="M18">
-        <v>100</v>
-      </c>
-      <c r="N18">
-        <v>100</v>
-      </c>
-      <c r="O18">
-        <v>76</v>
-      </c>
-      <c r="P18">
-        <v>90</v>
-      </c>
-      <c r="Q18">
-        <v>95</v>
-      </c>
-      <c r="R18">
-        <v>90</v>
-      </c>
-      <c r="S18">
-        <v>100</v>
-      </c>
-      <c r="T18">
-        <v>100</v>
-      </c>
       <c r="U18">
         <v>100</v>
       </c>
       <c r="V18">
-        <v>76</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -3976,7 +4000,7 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>95</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -3985,19 +4009,19 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N19">
         <v>100</v>
       </c>
       <c r="O19">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="P19">
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>95</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -4006,13 +4030,13 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U19">
         <v>100</v>
       </c>
       <c r="V19">
-        <v>92</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4053,13 +4077,13 @@
         <v>100</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N20">
         <v>100</v>
       </c>
       <c r="O20">
-        <v>92</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -4074,13 +4098,13 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U20">
         <v>100</v>
       </c>
       <c r="V20">
-        <v>92</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4109,46 +4133,46 @@
         <v>64</v>
       </c>
       <c r="I21">
-        <v>95</v>
+        <v>80.5</v>
       </c>
       <c r="J21">
-        <v>85</v>
+        <v>83.8</v>
       </c>
       <c r="K21">
-        <v>85</v>
+        <v>80.5</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M21">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="N21">
         <v>100</v>
       </c>
       <c r="O21">
-        <v>64</v>
+        <v>68.8</v>
       </c>
       <c r="P21">
-        <v>95</v>
+        <v>80.5</v>
       </c>
       <c r="Q21">
-        <v>85</v>
+        <v>83.8</v>
       </c>
       <c r="R21">
-        <v>85</v>
+        <v>80.5</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T21">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="U21">
         <v>100</v>
       </c>
       <c r="V21">
-        <v>64</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4177,46 +4201,46 @@
         <v>72</v>
       </c>
       <c r="I22">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="J22">
-        <v>85</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="L22">
         <v>100</v>
       </c>
       <c r="M22">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N22">
         <v>100</v>
       </c>
       <c r="O22">
-        <v>72</v>
+        <v>87.5</v>
       </c>
       <c r="P22">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="Q22">
-        <v>85</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S22">
         <v>100</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="U22">
         <v>100</v>
       </c>
       <c r="V22">
-        <v>72</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -4245,13 +4269,13 @@
         <v>96</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="J23">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -4263,16 +4287,16 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -4284,7 +4308,7 @@
         <v>100</v>
       </c>
       <c r="V23">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4313,46 +4337,46 @@
         <v>72</v>
       </c>
       <c r="I24">
-        <v>15</v>
+        <v>46.3</v>
       </c>
       <c r="J24">
-        <v>85</v>
+        <v>86.5</v>
       </c>
       <c r="K24">
-        <v>85</v>
+        <v>80.5</v>
       </c>
       <c r="L24">
-        <v>62.5</v>
+        <v>81.3</v>
       </c>
       <c r="M24">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="N24">
         <v>100</v>
       </c>
       <c r="O24">
-        <v>72</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="P24">
-        <v>15</v>
+        <v>46.3</v>
       </c>
       <c r="Q24">
-        <v>85</v>
+        <v>86.5</v>
       </c>
       <c r="R24">
-        <v>85</v>
+        <v>80.5</v>
       </c>
       <c r="S24">
-        <v>62.5</v>
+        <v>81.3</v>
       </c>
       <c r="T24">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="U24">
         <v>100</v>
       </c>
       <c r="V24">
-        <v>72</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -4381,46 +4405,46 @@
         <v>76</v>
       </c>
       <c r="I25">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="J25">
-        <v>85</v>
+        <v>89.2</v>
       </c>
       <c r="K25">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N25">
         <v>100</v>
       </c>
       <c r="O25">
-        <v>76</v>
+        <v>79.2</v>
       </c>
       <c r="P25">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q25">
-        <v>85</v>
+        <v>89.2</v>
       </c>
       <c r="R25">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S25">
         <v>100</v>
       </c>
       <c r="T25">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U25">
         <v>100</v>
       </c>
       <c r="V25">
-        <v>76</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -4449,46 +4473,46 @@
         <v>80</v>
       </c>
       <c r="I26">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="J26">
-        <v>90</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="K26">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N26">
         <v>100</v>
       </c>
       <c r="O26">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="P26">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q26">
-        <v>90</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="R26">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T26">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U26">
         <v>100</v>
       </c>
       <c r="V26">
-        <v>80</v>
+        <v>83.3</v>
       </c>
     </row>
   </sheetData>
@@ -4545,7 +4569,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>48</v>
@@ -4554,19 +4578,19 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>39.1</v>
+        <v>56.5</v>
       </c>
       <c r="G2" s="2">
-        <v>60.9</v>
+        <v>43.5</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4586,19 +4610,19 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>47.8</v>
+        <v>65.2</v>
       </c>
       <c r="G3" s="2">
-        <v>52.2</v>
+        <v>34.8</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4609,7 +4633,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -4618,19 +4642,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>60.9</v>
+        <v>87</v>
       </c>
       <c r="G4" s="2">
-        <v>39.1</v>
+        <v>13</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4650,16 +4674,16 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>82.59999999999999</v>
+        <v>87</v>
       </c>
       <c r="G5" s="2">
-        <v>17.4</v>
+        <v>13</v>
       </c>
       <c r="H5">
         <v>7.8</v>
@@ -4676,25 +4700,25 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>23</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>82.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="G6" s="2">
-        <v>17.4</v>
+        <v>4.3</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4705,7 +4729,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>52</v>
@@ -4714,19 +4738,19 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>87</v>
+        <v>95.7</v>
       </c>
       <c r="G7" s="2">
-        <v>13</v>
+        <v>4.3</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4746,19 +4770,19 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4808,7 +4832,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4840,22 +4864,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920183</v>
+        <v>22330051920177</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4863,19 +4887,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920183</v>
+        <v>22330051920177</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>48</v>
@@ -4892,16 +4916,16 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4915,13 +4939,13 @@
         <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>48</v>
@@ -4932,16 +4956,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920413</v>
+        <v>22330051920359</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4955,19 +4979,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920413</v>
+        <v>22330051920359</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>48</v>
@@ -4978,22 +5002,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920184</v>
+        <v>22330051920192</v>
       </c>
       <c r="B8" t="s">
         <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5001,22 +5025,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920190</v>
+        <v>22330051920192</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5024,16 +5048,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920378</v>
+        <v>22330051920193</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -5047,19 +5071,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920180</v>
+        <v>22330051920193</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>48</v>
@@ -5070,24 +5094,139 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920363</v>
+        <v>21330051920007</v>
       </c>
       <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920190</v>
+      </c>
+      <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920413</v>
+      </c>
+      <c r="B14" t="s">
         <v>65</v>
       </c>
-      <c r="C12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12">
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920378</v>
+      </c>
+      <c r="B15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920201</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920202</v>
+      </c>
+      <c r="B17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEV - Estadisticos 20232.xlsx
+++ b/grupos/4AEV - Estadisticos 20232.xlsx
@@ -4316,7 +4316,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="C24">
         <v>85</v>
@@ -4337,7 +4337,7 @@
         <v>72</v>
       </c>
       <c r="I24">
-        <v>46.3</v>
+        <v>80.5</v>
       </c>
       <c r="J24">
         <v>86.5</v>
@@ -4358,7 +4358,7 @@
         <v>77.09999999999999</v>
       </c>
       <c r="P24">
-        <v>46.3</v>
+        <v>80.5</v>
       </c>
       <c r="Q24">
         <v>86.5</v>

--- a/grupos/4AEV - Estadisticos 20232.xlsx
+++ b/grupos/4AEV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="87">
   <si>
     <t>Materia</t>
   </si>
@@ -170,18 +170,18 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
+    <t>Urias Morales Alejandra</t>
+  </si>
+  <si>
     <t>Sanchez Hernández Raymundo</t>
   </si>
   <si>
-    <t>Urias Morales Alejandra</t>
+    <t>Flores Paz Victor</t>
   </si>
   <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>Flores Paz Victor</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -194,13 +194,22 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>CAMPOS</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>MENDOZA</t>
@@ -209,19 +218,16 @@
     <t>MOLINA</t>
   </si>
   <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
   </si>
   <si>
     <t>CABRERA</t>
@@ -230,25 +236,25 @@
     <t>ROJAS</t>
   </si>
   <si>
-    <t>TIZA</t>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
   </si>
   <si>
     <t>MARCO</t>
@@ -257,7 +263,10 @@
     <t>DAVID</t>
   </si>
   <si>
-    <t>CRISTIAN OSMAR</t>
+    <t>FABIAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
   </si>
   <si>
     <t>ERIK OMAR</t>
@@ -266,22 +275,10 @@
     <t>VICTOR MANUEL</t>
   </si>
   <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>FABIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>ERIK</t>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
   </si>
 </sst>
 </file>
@@ -829,31 +826,31 @@
         <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -918,40 +915,40 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>7</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB5">
         <v>6</v>
@@ -1007,25 +1004,25 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1046,7 +1043,7 @@
         <v>10</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1096,25 +1093,25 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>5</v>
@@ -1129,7 +1126,7 @@
         <v>5</v>
       </c>
       <c r="AA7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB7">
         <v>6</v>
@@ -1185,25 +1182,25 @@
         <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1215,13 +1212,13 @@
         <v>9</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA8">
         <v>8</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>7</v>
@@ -1274,25 +1271,25 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1304,13 +1301,13 @@
         <v>9</v>
       </c>
       <c r="Z9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA9">
         <v>9</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC9">
         <v>7</v>
@@ -1363,31 +1360,31 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>10</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1399,7 +1396,7 @@
         <v>9</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC10">
         <v>7</v>
@@ -1452,25 +1449,25 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1491,7 +1488,7 @@
         <v>10</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1541,40 +1538,40 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z12">
         <v>6</v>
       </c>
       <c r="AA12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB12">
         <v>7</v>
@@ -1630,31 +1627,31 @@
         <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>7</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1663,13 +1660,13 @@
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB13">
         <v>7</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1719,25 +1716,25 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1746,7 +1743,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>5</v>
@@ -1758,7 +1755,7 @@
         <v>7</v>
       </c>
       <c r="AC14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1808,46 +1805,46 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>7</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB15">
         <v>6</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1897,46 +1894,46 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB16">
         <v>8</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1986,28 +1983,28 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -2019,10 +2016,10 @@
         <v>6</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC17">
         <v>5</v>
@@ -2075,25 +2072,25 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2105,7 +2102,7 @@
         <v>7</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA18">
         <v>7</v>
@@ -2164,34 +2161,34 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>9</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>8</v>
@@ -2203,7 +2200,7 @@
         <v>9</v>
       </c>
       <c r="AC19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2253,25 +2250,25 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2292,7 +2289,7 @@
         <v>8</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2342,25 +2339,25 @@
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>6</v>
@@ -2372,16 +2369,16 @@
         <v>6</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB21">
         <v>6</v>
       </c>
       <c r="AC21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2431,25 +2428,25 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2458,10 +2455,10 @@
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>8</v>
@@ -2520,25 +2517,25 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2547,7 +2544,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z23">
         <v>8</v>
@@ -2559,7 +2556,7 @@
         <v>7</v>
       </c>
       <c r="AC23">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2609,46 +2606,46 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>7</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z24">
         <v>5</v>
       </c>
       <c r="AA24">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>8</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2698,46 +2695,46 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>7</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA25">
         <v>8</v>
       </c>
       <c r="AB25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC25">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2787,25 +2784,25 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2814,10 +2811,10 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA26">
         <v>9</v>
@@ -2826,7 +2823,7 @@
         <v>7</v>
       </c>
       <c r="AC26">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2998,25 +2995,25 @@
         <v>50</v>
       </c>
       <c r="P4">
-        <v>78</v>
+        <v>85.7</v>
       </c>
       <c r="Q4">
-        <v>83.8</v>
+        <v>83</v>
       </c>
       <c r="R4">
-        <v>82.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="S4">
         <v>100</v>
       </c>
       <c r="T4">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="U4">
         <v>100</v>
       </c>
       <c r="V4">
-        <v>50</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3066,25 +3063,25 @@
         <v>72.90000000000001</v>
       </c>
       <c r="P5">
-        <v>82.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="Q5">
-        <v>83.8</v>
+        <v>87.2</v>
       </c>
       <c r="R5">
-        <v>87.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="S5">
-        <v>62.5</v>
+        <v>47.9</v>
       </c>
       <c r="T5">
-        <v>98</v>
+        <v>93.8</v>
       </c>
       <c r="U5">
         <v>100</v>
       </c>
       <c r="V5">
-        <v>72.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3146,7 +3143,7 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -3202,25 +3199,25 @@
         <v>56.3</v>
       </c>
       <c r="P7">
-        <v>82.90000000000001</v>
+        <v>58.7</v>
       </c>
       <c r="Q7">
-        <v>83.8</v>
+        <v>83</v>
       </c>
       <c r="R7">
-        <v>78</v>
+        <v>55.6</v>
       </c>
       <c r="S7">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="T7">
-        <v>86</v>
+        <v>53.8</v>
       </c>
       <c r="U7">
         <v>100</v>
       </c>
       <c r="V7">
-        <v>56.3</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3270,25 +3267,25 @@
         <v>87.5</v>
       </c>
       <c r="P8">
-        <v>90.2</v>
+        <v>90.5</v>
       </c>
       <c r="Q8">
-        <v>94.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="R8">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="S8">
         <v>100</v>
       </c>
       <c r="T8">
-        <v>96</v>
+        <v>92.5</v>
       </c>
       <c r="U8">
         <v>100</v>
       </c>
       <c r="V8">
-        <v>87.5</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3338,25 +3335,25 @@
         <v>93.8</v>
       </c>
       <c r="P9">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q9">
-        <v>91.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="S9">
         <v>100</v>
       </c>
       <c r="T9">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="U9">
         <v>100</v>
       </c>
       <c r="V9">
-        <v>93.8</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3406,25 +3403,25 @@
         <v>91.7</v>
       </c>
       <c r="P10">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q10">
-        <v>91.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="R10">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="S10">
         <v>100</v>
       </c>
       <c r="T10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U10">
         <v>100</v>
       </c>
       <c r="V10">
-        <v>91.7</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3474,10 +3471,10 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>95.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="Q11">
-        <v>94.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -3486,7 +3483,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -3542,25 +3539,25 @@
         <v>79.2</v>
       </c>
       <c r="P12">
-        <v>85.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="Q12">
-        <v>94.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="R12">
-        <v>90.2</v>
+        <v>90.5</v>
       </c>
       <c r="S12">
         <v>100</v>
       </c>
       <c r="T12">
-        <v>86</v>
+        <v>88.8</v>
       </c>
       <c r="U12">
         <v>100</v>
       </c>
       <c r="V12">
-        <v>79.2</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3610,25 +3607,25 @@
         <v>70.8</v>
       </c>
       <c r="P13">
-        <v>85.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="Q13">
-        <v>86.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="R13">
-        <v>92.7</v>
+        <v>90.5</v>
       </c>
       <c r="S13">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="T13">
-        <v>94</v>
+        <v>81.3</v>
       </c>
       <c r="U13">
         <v>100</v>
       </c>
       <c r="V13">
-        <v>70.8</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -3678,25 +3675,25 @@
         <v>66.7</v>
       </c>
       <c r="P14">
-        <v>80.5</v>
+        <v>85.7</v>
       </c>
       <c r="Q14">
-        <v>89.2</v>
+        <v>87.2</v>
       </c>
       <c r="R14">
-        <v>85.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="S14">
-        <v>50</v>
+        <v>54.2</v>
       </c>
       <c r="T14">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="U14">
         <v>100</v>
       </c>
       <c r="V14">
-        <v>66.7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3746,25 +3743,25 @@
         <v>87.5</v>
       </c>
       <c r="P15">
-        <v>87.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q15">
-        <v>86.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="S15">
         <v>100</v>
       </c>
       <c r="T15">
-        <v>92</v>
+        <v>92.5</v>
       </c>
       <c r="U15">
         <v>100</v>
       </c>
       <c r="V15">
-        <v>87.5</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -3814,25 +3811,25 @@
         <v>83.3</v>
       </c>
       <c r="P16">
-        <v>95.09999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="Q16">
-        <v>94.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="R16">
-        <v>95.09999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="S16">
-        <v>65.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="T16">
-        <v>92</v>
+        <v>88.8</v>
       </c>
       <c r="U16">
         <v>100</v>
       </c>
       <c r="V16">
-        <v>83.3</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3882,25 +3879,25 @@
         <v>87.5</v>
       </c>
       <c r="P17">
-        <v>95.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="Q17">
-        <v>89.2</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="R17">
-        <v>92.7</v>
+        <v>90.5</v>
       </c>
       <c r="S17">
         <v>100</v>
       </c>
       <c r="T17">
-        <v>98</v>
+        <v>92.5</v>
       </c>
       <c r="U17">
         <v>100</v>
       </c>
       <c r="V17">
-        <v>87.5</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -3950,25 +3947,25 @@
         <v>66.7</v>
       </c>
       <c r="P18">
-        <v>95.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="Q18">
-        <v>97.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R18">
-        <v>87.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="S18">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T18">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="U18">
         <v>100</v>
       </c>
       <c r="V18">
-        <v>66.7</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4021,7 +4018,7 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>94.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -4030,13 +4027,13 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="U19">
         <v>100</v>
       </c>
       <c r="V19">
-        <v>95.8</v>
+        <v>97.59999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4086,25 +4083,25 @@
         <v>97.90000000000001</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q20">
         <v>100</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S20">
         <v>100</v>
       </c>
       <c r="T20">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="U20">
         <v>100</v>
       </c>
       <c r="V20">
-        <v>97.90000000000001</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4154,25 +4151,25 @@
         <v>68.8</v>
       </c>
       <c r="P21">
-        <v>80.5</v>
+        <v>85.7</v>
       </c>
       <c r="Q21">
-        <v>83.8</v>
+        <v>83</v>
       </c>
       <c r="R21">
-        <v>80.5</v>
+        <v>85.7</v>
       </c>
       <c r="S21">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T21">
-        <v>78</v>
+        <v>86.3</v>
       </c>
       <c r="U21">
         <v>100</v>
       </c>
       <c r="V21">
-        <v>68.8</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4222,25 +4219,25 @@
         <v>87.5</v>
       </c>
       <c r="P22">
-        <v>95.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="Q22">
-        <v>91.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="R22">
-        <v>95.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="S22">
         <v>100</v>
       </c>
       <c r="T22">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="U22">
         <v>100</v>
       </c>
       <c r="V22">
-        <v>87.5</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -4290,13 +4287,13 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>97.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="Q23">
-        <v>97.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R23">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -4358,25 +4355,25 @@
         <v>77.09999999999999</v>
       </c>
       <c r="P24">
-        <v>80.5</v>
+        <v>85.7</v>
       </c>
       <c r="Q24">
-        <v>86.5</v>
+        <v>87.2</v>
       </c>
       <c r="R24">
-        <v>80.5</v>
+        <v>85.7</v>
       </c>
       <c r="S24">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="T24">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="U24">
         <v>100</v>
       </c>
       <c r="V24">
-        <v>77.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -4426,25 +4423,25 @@
         <v>79.2</v>
       </c>
       <c r="P25">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q25">
-        <v>89.2</v>
+        <v>91.5</v>
       </c>
       <c r="R25">
-        <v>95.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="S25">
         <v>100</v>
       </c>
       <c r="T25">
-        <v>98</v>
+        <v>88.8</v>
       </c>
       <c r="U25">
         <v>100</v>
       </c>
       <c r="V25">
-        <v>79.2</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -4494,25 +4491,25 @@
         <v>83.3</v>
       </c>
       <c r="P26">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q26">
-        <v>91.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="R26">
-        <v>95.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="S26">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T26">
-        <v>98</v>
+        <v>88.8</v>
       </c>
       <c r="U26">
         <v>100</v>
       </c>
       <c r="V26">
-        <v>83.3</v>
+        <v>90.5</v>
       </c>
     </row>
   </sheetData>
@@ -4578,19 +4575,19 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>56.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>43.5</v>
+        <v>30.4</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4610,19 +4607,19 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>65.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>34.8</v>
+        <v>26.1</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4633,7 +4630,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -4642,19 +4639,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>87</v>
+        <v>91.3</v>
       </c>
       <c r="G4" s="2">
-        <v>13</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4665,7 +4662,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -4674,19 +4671,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>87</v>
+        <v>95.7</v>
       </c>
       <c r="G5" s="2">
-        <v>13</v>
+        <v>4.3</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4700,7 +4697,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>23</v>
@@ -4718,7 +4715,7 @@
         <v>4.3</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4729,7 +4726,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>52</v>
@@ -4750,7 +4747,7 @@
         <v>4.3</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4761,7 +4758,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>53</v>
@@ -4770,19 +4767,19 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4832,7 +4829,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4864,7 +4861,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920177</v>
+        <v>21330051920007</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
@@ -4876,10 +4873,10 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4887,7 +4884,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920177</v>
+        <v>21330051920007</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -4910,7 +4907,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920188</v>
+        <v>22330051920190</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -4922,10 +4919,10 @@
         <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4933,7 +4930,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920188</v>
+        <v>22330051920190</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -4956,7 +4953,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920359</v>
+        <v>22330051920177</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
@@ -4968,10 +4965,10 @@
         <v>79</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4979,16 +4976,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920359</v>
+        <v>22330051920188</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -5002,22 +4999,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920192</v>
+        <v>22330051920413</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5025,22 +5022,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920192</v>
+        <v>22330051920378</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5048,22 +5045,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920193</v>
+        <v>22330051920192</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5074,13 +5071,13 @@
         <v>22330051920193</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -5094,22 +5091,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920007</v>
+        <v>22330051920356</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5117,16 +5114,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920190</v>
+        <v>22330051920371</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -5135,98 +5132,6 @@
         <v>49</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920413</v>
-      </c>
-      <c r="B14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920378</v>
-      </c>
-      <c r="B15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" t="s">
-        <v>85</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920201</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920202</v>
-      </c>
-      <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17">
         <v>5</v>
       </c>
     </row>
